--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Spaceman Spiff</v>
+        <v>Kid Onion Alien</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Kid Onion Alien</v>
+        <v>Spellbinder</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Spellbinder</v>
+        <v>Baby Gao</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Baby Gao</v>
+        <v>Sweaty Diver</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Sweaty Diver</v>
+        <v>Zorro</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Zorro</v>
+        <v>Kolmisilma</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Kolmisilma</v>
+        <v>Spartan</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Spartan</v>
+        <v>noita crown and amulet</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>noita crown and amulet</v>
+        <v>Tenna</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Tenna</v>
+        <v>Ming Ming</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ming Ming</v>
+        <v>Helldiver Helmet</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Helldiver Helmet</v>
+        <v>Aries Horns</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Aries Horns</v>
+        <v>Lagavulin Hat</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Lagavulin Hat</v>
+        <v>Jimbo</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jimbo</v>
+        <v xml:space="preserve">Cartethiya </v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v xml:space="preserve">Cartethiya </v>
+        <v>Beach set?</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Beach set?</v>
+        <v>Chiikawa</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Chiikawa</v>
+        <v>Completely not suspicious at all hat - Blue</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Completely not suspicious at all hat - Blue</v>
+        <v>AIO Cooler</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AIO Cooler</v>
+        <v>Water Princess</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Water Princess</v>
+        <v>Garen (Hair and Pauldrons)</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Garen (Hair and Pauldrons)</v>
+        <v>Falcon</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Falcon</v>
+        <v>Galaxy Brain</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Galaxy Brain</v>
+        <v>Ryuu Lion</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ryuu Lion</v>
+        <v>Avatar Pavi</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Avatar Pavi</v>
+        <v>Voli</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Voli</v>
+        <v>PLAYERUNKNOWN Skin</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>PLAYERUNKNOWN Skin</v>
+        <v>Bacon Hair</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Bacon Hair</v>
+        <v>Cone of shame</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Cone of shame</v>
+        <v>Crab Hat</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Crab Hat</v>
+        <v>Rose</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Rose</v>
+        <v>Altar Set</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Altar Set</v>
+        <v>Tuck</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Tuck</v>
+        <v>Coraline</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Coraline</v>
+        <v>Kafka Hibino</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Kafka Hibino</v>
+        <v>Urahara Kisuke Hat</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Urahara Kisuke Hat</v>
+        <v>Dark Halo</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Dark Halo</v>
+        <v>Sherma</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Sherma</v>
+        <v>Broken Image Icon</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Broken Image Icon</v>
+        <v>Ironclad</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ironclad</v>
+        <v>Brewman</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Brewman</v>
+        <v>Brewman (links are messed up, grabbed from discord instead)</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Brewman (links are messed up, grabbed from discord instead)</v>
+        <v>Ponyo</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ponyo</v>
+        <v>Sonia</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Sonia</v>
+        <v>Grim</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Grim</v>
+        <v>Braum</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Braum</v>
+        <v>Fly Agaric Hat + Minecraft soil</v>
       </c>
     </row>
   </sheetData>
